--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>2.98</v>
       </c>
       <c r="J3" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
         <v>4.9</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 01:39:42</t>
+          <t>2026-03-28 03:54:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
         <v>2.36</v>
@@ -1154,13 +1154,13 @@
         <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 03:54:22</t>
+          <t>2026-03-28 06:09:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 06:09:12</t>
+          <t>2026-03-28 08:24:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 08:24:38</t>
+          <t>2026-03-28 21:17:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.86</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2.98</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 08:24:38</t>
+          <t>2026-03-28 21:17:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,378 +1131,1154 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
         <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 08:24:38</t>
+          <t>2026-03-28 21:17:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Arezzo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ascoli</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-28 21:17:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-28 21:17:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-28 21:17:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-28 21:17:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Deportivo Recoleta</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="L9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-28 08:24:38</t>
+      <c r="O9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-28 21:17:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,103 +757,103 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.84</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.79</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -862,7 +862,7 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
         <v>1.03</v>
@@ -916,11 +916,11 @@
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
         <v>1.66</v>
@@ -963,67 +963,67 @@
         <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1041,7 +1041,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK3" t="n">
         <v>25</v>
@@ -1107,14 +1107,14 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
         <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
         <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>1.96</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1256,7 +1256,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>1.03</v>
@@ -1265,10 +1265,10 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AV4" t="n">
         <v>1.03</v>
@@ -1277,10 +1277,10 @@
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.03</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1387,10 +1387,10 @@
         <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1453,10 +1453,10 @@
         <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
         <v>5.6</v>
@@ -1465,10 +1465,10 @@
         <v>5.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
@@ -1477,32 +1477,32 @@
         <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -1954,7 +1954,7 @@
         <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
@@ -2029,7 +2029,7 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AQ8" t="n">
         <v>9.4</v>
@@ -2038,10 +2038,10 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2053,7 +2053,7 @@
         <v>36</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
@@ -2062,7 +2062,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BB8" t="n">
         <v>21</v>
@@ -2074,7 +2074,7 @@
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BF8" t="n">
         <v>2.72</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-28 21:17:18</t>
+          <t>2026-03-28 23:25:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,73 +757,73 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
         <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
         <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -832,10 +832,10 @@
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG2" t="n">
         <v>23</v>
@@ -844,7 +844,7 @@
         <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -862,7 +862,7 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
         <v>1.03</v>
@@ -916,11 +916,11 @@
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -951,52 +951,52 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.5</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="U3" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
@@ -1008,7 +1008,7 @@
         <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z3" t="n">
         <v>90</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
@@ -1029,7 +1029,7 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1053,7 +1053,7 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1226,7 +1226,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY4" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H5" t="n">
         <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1381,13 +1381,13 @@
         <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
         <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
         <v>1.63</v>
@@ -1411,7 +1411,7 @@
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>75</v>
@@ -1450,7 +1450,7 @@
         <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
         <v>3.85</v>
@@ -1459,13 +1459,13 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
         <v>5.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AW5" t="n">
         <v>4.1</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1942,130 +1942,130 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.74</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
         <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.76</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.66</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
@@ -2074,17 +2074,17 @@
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.76</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.72</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.72</v>
+        <v>50</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,589 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-28 23:25:58</t>
+          <t>2026-03-29 01:34:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-29 01:34:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-29 01:34:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>22:20:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X12" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-29 01:34:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -766,10 +766,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
@@ -805,7 +805,7 @@
         <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.25</v>
@@ -814,7 +814,7 @@
         <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z2" t="n">
         <v>13.5</v>
@@ -865,62 +865,62 @@
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -975,7 +975,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O3" t="n">
         <v>1.5</v>
@@ -984,16 +984,16 @@
         <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
         <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="U3" t="n">
         <v>1.56</v>
@@ -1002,10 +1002,10 @@
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
         <v>23</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
         <v>42</v>
@@ -1029,92 +1029,92 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>1.34</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="n">
         <v>2.12</v>
@@ -1154,25 +1154,25 @@
         <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
         <v>1.7</v>
@@ -1181,16 +1181,16 @@
         <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1202,7 +1202,7 @@
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1214,7 +1214,7 @@
         <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1226,7 +1226,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1256,22 +1256,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
         <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
         <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW4" t="n">
         <v>4.2</v>
@@ -1283,7 +1283,7 @@
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
@@ -1301,14 +1301,14 @@
         <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
         <v>4.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1411,7 +1411,7 @@
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>75</v>
@@ -1420,13 +1420,13 @@
         <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
         <v>44</v>
@@ -1447,7 +1447,7 @@
         <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.6</v>
@@ -1459,13 +1459,13 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU5" t="n">
         <v>5.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW5" t="n">
         <v>4.1</v>
@@ -1486,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BD5" t="n">
         <v>4.1</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1560,19 +1560,19 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>3.6</v>
@@ -1945,13 +1945,13 @@
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
         <v>2.06</v>
@@ -1966,13 +1966,13 @@
         <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -1981,7 +1981,7 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
         <v>95</v>
@@ -1993,10 +1993,10 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
@@ -2008,7 +2008,7 @@
         <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
         <v>30</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>65</v>
@@ -2035,10 +2035,10 @@
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2050,7 +2050,7 @@
         <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2062,29 +2062,29 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
         <v>2.38</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>2.66</v>
@@ -2527,34 +2527,34 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P11" t="n">
         <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2617,7 +2617,7 @@
         <v>6</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
         <v>4</v>
@@ -2638,7 +2638,7 @@
         <v>3.75</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
         <v>3.75</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
         <v>1.62</v>
@@ -2712,31 +2712,31 @@
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
         <v>1.94</v>
@@ -2766,7 +2766,7 @@
         <v>8.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
         <v>36</v>
@@ -2808,13 +2808,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR12" t="n">
         <v>42</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT12" t="n">
         <v>5.3</v>
@@ -2826,7 +2826,7 @@
         <v>4</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
         <v>6.2</v>
@@ -2838,29 +2838,29 @@
         <v>4</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
         <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF12" t="n">
         <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
@@ -969,7 +969,7 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
@@ -981,7 +981,7 @@
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
         <v>2.24</v>
@@ -990,7 +990,7 @@
         <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
         <v>2.42</v>
@@ -1002,7 +1002,7 @@
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1062,7 +1062,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AR3" t="n">
         <v>1.19</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1184,7 +1184,7 @@
         <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.89</v>
@@ -1202,7 +1202,7 @@
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1226,7 +1226,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1259,10 +1259,10 @@
         <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
         <v>5.9</v>
@@ -1271,10 +1271,10 @@
         <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
         <v>8.199999999999999</v>
@@ -1283,32 +1283,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
         <v>2.64</v>
@@ -1387,16 +1387,16 @@
         <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -1560,13 +1560,13 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
         <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
         <v>4.1</v>
@@ -1951,7 +1951,7 @@
         <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
         <v>2.06</v>
@@ -1981,7 +1981,7 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
         <v>95</v>
@@ -2038,7 +2038,7 @@
         <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2062,10 +2062,10 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
         <v>6.8</v>
@@ -2074,17 +2074,17 @@
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2336,7 +2336,7 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H11" t="n">
         <v>2.38</v>
@@ -2515,7 +2515,7 @@
         <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -2715,13 +2715,13 @@
         <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.37</v>
@@ -2808,13 +2808,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR12" t="n">
         <v>42</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT12" t="n">
         <v>5.3</v>
@@ -2823,10 +2823,10 @@
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
         <v>6.2</v>
@@ -2850,17 +2850,17 @@
         <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF12" t="n">
         <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -787,7 +787,7 @@
         <v>1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
         <v>2.48</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -1002,7 +1002,7 @@
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,67 +1136,67 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1253,69 +1253,69 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Club El Porvenir</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1566,13 +1566,13 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.86</v>
+        <v>1.82</v>
       </c>
       <c r="G7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV7" t="n">
         <v>4.2</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.35</v>
       </c>
-      <c r="K8" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.06</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.88</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
         <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AO8" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
         <v>10</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>11</v>
-      </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>34</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>17.5</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2142,19 +2142,19 @@
         <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>2.48</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,78 +2489,78 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>3.95</v>
+        <v>2.88</v>
       </c>
       <c r="H11" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>1.76</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,10 +2569,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2611,69 +2611,69 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,184 +2683,1154 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22:20:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>2.92</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>2.26</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>2.98</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="K12" t="n">
         <v>4.6</v>
       </c>
       <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-29 07:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-29 07:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.35</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-29 07:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-29 07:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-29 07:59:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>22:20:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M17" t="n">
         <v>1.08</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="N17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.37</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P17" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q17" t="n">
         <v>2.08</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R17" t="n">
         <v>1.3</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S17" t="n">
         <v>3.3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T17" t="n">
         <v>1.94</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U17" t="n">
         <v>1.62</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V17" t="n">
         <v>1.11</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W17" t="n">
         <v>2.62</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X17" t="n">
         <v>970</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y17" t="n">
         <v>27</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z17" t="n">
         <v>80</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC17" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AD17" t="n">
         <v>36</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE17" t="n">
         <v>170</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AF17" t="n">
         <v>10</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AG17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AH17" t="n">
         <v>34</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AI17" t="n">
         <v>160</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AJ17" t="n">
         <v>970</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK17" t="n">
         <v>22</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AL17" t="n">
         <v>60</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ17" t="n">
         <v>3.95</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR17" t="n">
         <v>42</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS17" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AT17" t="n">
         <v>5.3</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AU17" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AV17" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AW17" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AX17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AY17" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="AZ17" t="n">
         <v>4</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BA17" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB17" t="n">
         <v>10</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BC17" t="n">
         <v>3.8</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BD17" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BE17" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BF17" t="n">
         <v>7.6</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BG17" t="n">
         <v>4.4</v>
       </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-03-29 05:51:01</t>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -951,67 +951,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
         <v>2.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="U3" t="n">
         <v>1.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Z3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1023,7 +1023,7 @@
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1044,7 +1044,7 @@
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>80</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="AY3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA3" t="n">
         <v>1.41</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BB3" t="n">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.34</v>
+        <v>1.88</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.82</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="n">
         <v>4.4</v>
@@ -1778,7 +1778,7 @@
         <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -2148,13 +2148,13 @@
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="R9" t="n">
         <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
         <v>2.48</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>2.66</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.44</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,7 +2357,7 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
         <v>1.38</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H11" t="n">
         <v>2.88</v>
@@ -2518,7 +2518,7 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2554,7 +2554,7 @@
         <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
         <v>1.51</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
         <v>1.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -3112,19 +3112,19 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
         <v>2.34</v>
@@ -3485,7 +3485,7 @@
         <v>2.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
         <v>3.55</v>
@@ -3497,7 +3497,7 @@
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
         <v>1.44</v>
@@ -3512,19 +3512,19 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="T16" t="n">
         <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
         <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
         <v>11.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -3667,34 +3667,34 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="G17" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="H17" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
         <v>1.81</v>
@@ -3703,134 +3703,134 @@
         <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
         <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AF17" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
         <v>970</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN17" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.95</v>
+        <v>1.68</v>
       </c>
       <c r="AR17" t="n">
-        <v>42</v>
+        <v>1.63</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.4</v>
+        <v>1.66</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.6</v>
+        <v>2.24</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>1.56</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>1.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>1.66</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>1.66</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G3" t="n">
         <v>1.53</v>
@@ -960,10 +960,10 @@
         <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
@@ -1008,7 +1008,7 @@
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1059,46 +1059,46 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AS3" t="n">
         <v>1.41</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
         <v>1.83</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AW3" t="n">
         <v>1.57</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA3" t="n">
         <v>1.41</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BD3" t="n">
         <v>1.39</v>
@@ -1107,14 +1107,14 @@
         <v>1.41</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1184,7 +1184,7 @@
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.06</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.89</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
         <v>9</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4</v>
       </c>
-      <c r="AR7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="BC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE7" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.2</v>
       </c>
-      <c r="BG7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV8" t="n">
         <v>4.5</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X8" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ8" t="n">
+      <c r="AW8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY8" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AZ8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>5.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,7 +2223,7 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.03</v>
@@ -2235,10 +2235,10 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
         <v>1.03</v>
@@ -2247,7 +2247,7 @@
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY9" t="n">
         <v>1.03</v>
@@ -2271,14 +2271,14 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
         <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -2697,100 +2697,100 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J12" t="n">
         <v>2.92</v>
       </c>
-      <c r="G12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.78</v>
-      </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>1.51</v>
+        <v>2.72</v>
       </c>
       <c r="O12" t="n">
         <v>1.49</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2799,43 +2799,43 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
@@ -2853,14 +2853,14 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>2.24</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
@@ -2924,7 +2924,7 @@
         <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
         <v>1.27</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -3491,13 +3491,13 @@
         <v>3.55</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
         <v>1.44</v>
@@ -3512,7 +3512,7 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.87</v>
@@ -3524,7 +3524,7 @@
         <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
         <v>11.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -3667,34 +3667,34 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
         <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
         <v>1.81</v>
@@ -3703,31 +3703,31 @@
         <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3751,10 +3751,10 @@
         <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ17" t="n">
         <v>970</v>
@@ -3772,52 +3772,52 @@
         <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.68</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="AS17" t="n">
         <v>1.66</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.24</v>
+        <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.67</v>
+        <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="BE17" t="n">
         <v>1.66</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="J2" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X2" t="n">
         <v>10.5</v>
       </c>
       <c r="Y2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR2" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AS2" t="n">
         <v>13</v>
       </c>
-      <c r="AE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AT2" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
@@ -951,34 +951,34 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G3" t="n">
         <v>1.53</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
         <v>13.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
         <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
         <v>1.6</v>
@@ -990,7 +990,7 @@
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.52</v>
@@ -999,7 +999,7 @@
         <v>1.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
         <v>2.88</v>
@@ -1008,10 +1008,10 @@
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1023,7 +1023,7 @@
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AT3" t="n">
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AV3" t="n">
         <v>2.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.84</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,78 +1131,78 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,22 +1211,22 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1354,7 +1354,7 @@
         <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,13 +1363,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Club El Porvenir</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1548,7 +1548,7 @@
         <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Club El Porvenir</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="K8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS8" t="n">
         <v>4.2</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BG8" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,72 +2101,72 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.75</v>
       </c>
-      <c r="G9" t="n">
+      <c r="Q9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.89</v>
       </c>
-      <c r="H9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.58</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="BF9" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,72 +2295,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>1.88</v>
       </c>
       <c r="H10" t="n">
-        <v>2.48</v>
+        <v>5.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="J10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.66</v>
       </c>
-      <c r="K10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.16</v>
-      </c>
       <c r="R10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.13</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.39</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,7 +2417,7 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.03</v>
@@ -2429,10 +2429,10 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
         <v>1.03</v>
@@ -2441,7 +2441,7 @@
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY10" t="n">
         <v>1.03</v>
@@ -2465,21 +2465,21 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82</v>
+        <v>3.65</v>
       </c>
       <c r="H11" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,34 +2527,34 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U11" t="n">
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,109 +2688,109 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="H12" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="I12" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.72</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7</v>
+        <v>1.76</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2799,43 +2799,43 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
@@ -2853,21 +2853,21 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="O13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.39</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY13" t="n">
         <v>12</v>
       </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CA Mineiro (W)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Sao Paulo (W)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3112,19 +3112,19 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
         <v>1.09</v>
       </c>
-      <c r="G15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.39</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,78 +3459,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.98</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.22</v>
+        <v>1.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,256 +3581,644 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-29 14:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-29 14:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>22:20:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Millonarios</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Fortaleza FC</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" t="n">
         <v>1.64</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="G19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I19" t="n">
         <v>7</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L19" t="n">
         <v>1.36</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M19" t="n">
         <v>1.08</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N19" t="n">
         <v>3.35</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O19" t="n">
         <v>1.37</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P19" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q19" t="n">
         <v>2.08</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S19" t="n">
         <v>3.35</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2.04</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>1.85</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V19" t="n">
         <v>1.16</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="W19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X19" t="n">
         <v>970</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y19" t="n">
         <v>23</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z19" t="n">
         <v>75</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
         <v>970</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC19" t="n">
         <v>10</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD19" t="n">
         <v>25</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE19" t="n">
         <v>130</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AF19" t="n">
         <v>970</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG19" t="n">
         <v>970</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AH19" t="n">
         <v>24</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AI19" t="n">
         <v>130</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AJ19" t="n">
         <v>970</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK19" t="n">
         <v>20</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AL19" t="n">
         <v>46</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AM19" t="n">
         <v>180</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AN19" t="n">
         <v>970</v>
       </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ19" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR19" t="n">
         <v>2.14</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AS19" t="n">
         <v>1.66</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AT19" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AU19" t="n">
         <v>4.4</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AV19" t="n">
         <v>2.06</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AW19" t="n">
         <v>3.5</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AX19" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AY19" t="n">
         <v>7.8</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="AZ19" t="n">
         <v>1.67</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BA19" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BB19" t="n">
         <v>12</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BC19" t="n">
         <v>2</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BD19" t="n">
         <v>2.14</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BE19" t="n">
         <v>1.66</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BF19" t="n">
         <v>9</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BG19" t="n">
         <v>1.66</v>
       </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-03-29 12:15:15</t>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Paradou</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.5</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>1.77</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.94</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X2" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AV2" t="n">
         <v>2.12</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>1.42</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="AY2" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>2.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>1.42</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>1.94</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>1.35</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>1.42</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>1.43</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,81 +937,81 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>870</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L3" t="n">
         <v>1.45</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="M3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N3" t="n">
         <v>1.1</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.52</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>2.88</v>
+        <v>1.63</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1023,7 +1023,7 @@
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>50</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1035,93 +1035,93 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.89</v>
+        <v>1.16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.12</v>
+        <v>1.05</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>1.17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.1</v>
+        <v>1.05</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.94</v>
+        <v>1.05</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,78 +1131,78 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,22 +1211,22 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1354,7 +1354,7 @@
         <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,13 +1363,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>Club El Porvenir</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1548,7 +1548,7 @@
         <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Club El Porvenir</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>2.64</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>1.89</v>
       </c>
       <c r="H8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT8" t="n">
         <v>3.5</v>
       </c>
-      <c r="I8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X8" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AX8" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AY8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>2.46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,72 +2101,72 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.74</v>
+        <v>2.46</v>
       </c>
       <c r="G9" t="n">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>1.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,72 +2295,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.66</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>5.8</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,7 +2417,7 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.03</v>
@@ -2429,10 +2429,10 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
         <v>1.03</v>
@@ -2441,7 +2441,7 @@
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
         <v>1.03</v>
@@ -2465,21 +2465,21 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,114 +2489,114 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H11" t="n">
         <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="J11" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.05</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.39</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2605,43 +2605,43 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS11" t="n">
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
         <v>1.03</v>
@@ -2659,21 +2659,21 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CA Mineiro (W)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Sao Paulo (W)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,22 +2721,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.21</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.76</v>
+        <v>1.21</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.55</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP13" t="n">
         <v>10</v>
       </c>
-      <c r="Y13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AQ13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AR13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="BC13" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="BD13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG13" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>44</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>28</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CA Mineiro (W)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sao Paulo (W)</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3112,19 +3112,19 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>1.37</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,78 +3459,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,69 +3581,69 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,572 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:20:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.09</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.09</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.39</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.39</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Central Espanol</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Deportivo Maldonado</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-03-29 14:21:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>22:20:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fortaleza FC</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I19" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="X19" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
         <v>1.53</v>
@@ -772,7 +772,7 @@
         <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -865,28 +865,28 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.74</v>
+        <v>5.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.42</v>
+        <v>2.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.85</v>
+        <v>4.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.12</v>
+        <v>5.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.42</v>
+        <v>2.32</v>
       </c>
       <c r="AX2" t="n">
         <v>3.55</v>
@@ -895,32 +895,32 @@
         <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.42</v>
+        <v>2.32</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.42</v>
+        <v>2.32</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
         <v>2.6</v>
@@ -960,7 +960,7 @@
         <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
         <v>2.96</v>
@@ -978,7 +978,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
         <v>1.46</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,10 +1253,10 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
         <v>1.03</v>
@@ -1265,10 +1265,10 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
         <v>1.03</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1533,61 +1533,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1733,13 +1733,13 @@
         <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
         <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
         <v>3.35</v>
@@ -1751,13 +1751,13 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
         <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
         <v>2.38</v>
@@ -1781,16 +1781,16 @@
         <v>1.62</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
         <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>9</v>
@@ -1799,40 +1799,40 @@
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
         <v>6.6</v>
@@ -1841,10 +1841,10 @@
         <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
@@ -1853,10 +1853,10 @@
         <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
@@ -1865,32 +1865,32 @@
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
         <v>4.8</v>
@@ -1939,7 +1939,7 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1951,7 +1951,7 @@
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -1960,22 +1960,22 @@
         <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
         <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,22 +1999,22 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2029,28 +2029,28 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS8" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS8" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AT8" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
         <v>7.8</v>
@@ -2059,32 +2059,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.05</v>
@@ -2166,7 +2166,7 @@
         <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
         <v>4.2</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H11" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -2530,13 +2530,13 @@
         <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
         <v>1.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -2545,7 +2545,7 @@
         <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
         <v>1.85</v>
@@ -2554,7 +2554,7 @@
         <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
         <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
@@ -2581,22 +2581,22 @@
         <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ11" t="n">
         <v>70</v>
       </c>
       <c r="AK11" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2620,53 +2620,53 @@
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>28</v>
+        <v>7.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -2853,14 +2853,14 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -2933,10 +2933,10 @@
         <v>3.95</v>
       </c>
       <c r="T13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
@@ -2954,7 +2954,7 @@
         <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
         <v>8.6</v>
@@ -2972,7 +2972,7 @@
         <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -2981,13 +2981,13 @@
         <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2996,7 +2996,7 @@
         <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3032,29 +3032,29 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF13" t="n">
         <v>17.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
         <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3590,7 +3590,7 @@
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
         <v>8</v>
@@ -3602,41 +3602,41 @@
         <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.36</v>
@@ -3694,28 +3694,28 @@
         <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
         <v>1.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
         <v>2.42</v>
@@ -3724,10 +3724,10 @@
         <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3748,22 +3748,22 @@
         <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
@@ -3778,13 +3778,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.36</v>
+        <v>5.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="AT17" t="n">
         <v>5.6</v>
@@ -3793,44 +3793,44 @@
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY17" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.69</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.34</v>
+        <v>5.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
         <v>2.6</v>
@@ -1059,22 +1059,22 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AS3" t="n">
         <v>1.05</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.24</v>
+        <v>1.16</v>
       </c>
       <c r="AV3" t="n">
         <v>1.05</v>
@@ -1083,10 +1083,10 @@
         <v>1.05</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AZ3" t="n">
         <v>1.05</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1166,25 +1166,25 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P4" t="n">
         <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1259,10 +1259,10 @@
         <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AT4" t="n">
         <v>4.4</v>
@@ -1271,44 +1271,44 @@
         <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1360,25 +1360,25 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="R5" t="n">
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1450,59 +1450,59 @@
         <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BF5" t="n">
         <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
         <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1596,7 +1596,7 @@
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6</v>
       </c>
-      <c r="BF6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1730,55 +1730,55 @@
         <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
         <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
         <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X7" t="n">
         <v>17</v>
@@ -1787,7 +1787,7 @@
         <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -1844,7 +1844,7 @@
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
@@ -1856,7 +1856,7 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
@@ -1868,29 +1868,29 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
         <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.5</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
         <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
@@ -1945,37 +1945,37 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1999,13 +1999,13 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
         <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2035,10 +2035,10 @@
         <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="AT8" t="n">
         <v>4.4</v>
@@ -2047,22 +2047,22 @@
         <v>4.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW8" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
         <v>7.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
@@ -2071,20 +2071,20 @@
         <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
         <v>11</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H9" t="n">
         <v>2.52</v>
@@ -2127,25 +2127,25 @@
         <v>3.55</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
         <v>2.2</v>
@@ -2163,11 +2163,11 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.39</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2229,7 +2229,7 @@
         <v>5.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AS9" t="n">
         <v>1.55</v>
@@ -2250,13 +2250,13 @@
         <v>1.56</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BB9" t="n">
         <v>1.55</v>
@@ -2265,7 +2265,7 @@
         <v>1.55</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BE9" t="n">
         <v>1.56</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
         <v>3.15</v>
@@ -2321,10 +2321,10 @@
         <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2336,25 +2336,25 @@
         <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
         <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
         <v>1.38</v>
@@ -2378,7 +2378,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AR10" t="n">
         <v>3.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AV10" t="n">
         <v>4.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>2.76</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
         <v>3.35</v>
@@ -2554,7 +2554,7 @@
         <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
         <v>10</v>
@@ -2563,7 +2563,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA11" t="n">
         <v>44</v>
@@ -2590,16 +2590,16 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="AJ11" t="n">
         <v>70</v>
       </c>
       <c r="AK11" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2632,13 +2632,13 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX11" t="n">
         <v>17</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>17.5</v>
@@ -2653,20 +2653,20 @@
         <v>8</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
         <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -2697,103 +2697,103 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>5.2</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>1.21</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2802,65 +2802,65 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -2933,10 +2933,10 @@
         <v>3.95</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
@@ -2969,7 +2969,7 @@
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
@@ -3008,7 +3008,7 @@
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3032,7 +3032,7 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB13" t="n">
         <v>8</v>
@@ -3044,7 +3044,7 @@
         <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13" t="n">
         <v>17.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G17" t="n">
         <v>1.69</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
@@ -3691,22 +3691,22 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q17" t="n">
         <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
         <v>2.08</v>
@@ -3739,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>120</v>
@@ -3775,7 +3775,7 @@
         <v>180</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AQ17" t="n">
         <v>4.7</v>
@@ -3796,7 +3796,7 @@
         <v>4.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AX17" t="n">
         <v>7</v>
@@ -3808,7 +3808,7 @@
         <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -814,7 +814,7 @@
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Z2" t="n">
         <v>110</v>
@@ -829,7 +829,7 @@
         <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -841,7 +841,7 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
         <v>3.3</v>
@@ -1002,7 +1002,7 @@
         <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.08</v>
@@ -1178,19 +1178,19 @@
         <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1363,28 +1363,28 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.39</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
         <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
@@ -1748,28 +1748,28 @@
         <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
         <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
         <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
         <v>1.83</v>
@@ -1778,13 +1778,13 @@
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X7" t="n">
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="Z7" t="n">
         <v>90</v>
@@ -1799,7 +1799,7 @@
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -1808,22 +1808,22 @@
         <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
@@ -1844,7 +1844,7 @@
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
@@ -1856,41 +1856,41 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="AZ7" t="n">
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB7" t="n">
         <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
         <v>6.6</v>
@@ -1972,7 +1972,7 @@
         <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -1981,7 +1981,7 @@
         <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2002,7 +2002,7 @@
         <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="AH8" t="n">
         <v>60</v>
@@ -2035,22 +2035,22 @@
         <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
         <v>7.8</v>
@@ -2059,10 +2059,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
@@ -2071,20 +2071,20 @@
         <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BF8" t="n">
         <v>11</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G9" t="n">
         <v>3.55</v>
@@ -2130,7 +2130,7 @@
         <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,10 +2139,10 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
         <v>1.51</v>
@@ -2151,22 +2151,22 @@
         <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
         <v>3.15</v>
@@ -2330,13 +2330,13 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
         <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
         <v>1.81</v>
@@ -2351,7 +2351,7 @@
         <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
         <v>2.14</v>
@@ -2360,7 +2360,7 @@
         <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY10" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
         <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
@@ -2536,13 +2536,13 @@
         <v>1.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T11" t="n">
         <v>1.98</v>
@@ -2569,7 +2569,7 @@
         <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
@@ -2632,7 +2632,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>17</v>
@@ -2644,29 +2644,29 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2805,25 +2805,25 @@
         <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR12" t="n">
         <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
         <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW12" t="n">
         <v>5.5</v>
@@ -2856,11 +2856,11 @@
         <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H13" t="n">
         <v>3.9</v>
@@ -2906,7 +2906,7 @@
         <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2942,7 +2942,7 @@
         <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="X13" t="n">
         <v>14</v>
@@ -3035,7 +3035,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -3085,58 +3085,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,34 +3303,34 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="O15" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.39</v>
+        <v>2.32</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -3473,67 +3473,67 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="J16" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
         <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3542,10 +3542,10 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3557,7 +3557,7 @@
         <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3590,53 +3590,53 @@
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
         <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>1.69</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.36</v>
@@ -3691,13 +3691,13 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
         <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
         <v>2.1</v>
@@ -3712,13 +3712,13 @@
         <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -3760,13 +3760,13 @@
         <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
         <v>970</v>
@@ -3775,62 +3775,62 @@
         <v>180</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AX17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>3.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.6</v>
+        <v>3.95</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="BF17" t="n">
         <v>9</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -784,34 +784,34 @@
         <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P2" t="n">
         <v>1.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
         <v>2.52</v>
       </c>
       <c r="U2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
         <v>2.84</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
         <v>950</v>
@@ -850,7 +850,7 @@
         <v>970</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
         <v>80</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AU2" t="n">
         <v>4.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -951,82 +951,82 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
         <v>1.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1047,7 +1047,7 @@
         <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.05</v>
+        <v>3.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.16</v>
+        <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.05</v>
+        <v>3.75</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1166,19 +1166,19 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P4" t="n">
         <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1339,103 +1339,103 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J5" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>2.16</v>
       </c>
       <c r="O5" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1450,59 +1450,59 @@
         <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
@@ -1805,7 +1805,7 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG7" t="n">
         <v>9.6</v>
@@ -1817,7 +1817,7 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -1838,16 +1838,16 @@
         <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
         <v>5.4</v>
@@ -1856,7 +1856,7 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
@@ -1868,7 +1868,7 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB7" t="n">
         <v>6.4</v>
@@ -1877,7 +1877,7 @@
         <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE7" t="n">
         <v>6</v>
@@ -1886,11 +1886,11 @@
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1921,46 +1921,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
         <v>1.9</v>
@@ -1969,10 +1969,10 @@
         <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -2002,7 +2002,7 @@
         <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH8" t="n">
         <v>60</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
@@ -2038,25 +2038,25 @@
         <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
         <v>4.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW8" t="n">
         <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>6.8</v>
@@ -2068,23 +2068,23 @@
         <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BF8" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
         <v>2.84</v>
@@ -2142,10 +2142,10 @@
         <v>2.42</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
         <v>2.2</v>
@@ -2166,7 +2166,7 @@
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,7 +2333,7 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
@@ -2342,25 +2342,25 @@
         <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
         <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="AS10" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AT10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU10" t="n">
         <v>4.5</v>
       </c>
-      <c r="AU10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AV10" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.9</v>
+        <v>2.28</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.65</v>
+        <v>2.44</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -2509,10 +2509,10 @@
         <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
@@ -2527,16 +2527,16 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
@@ -2569,7 +2569,7 @@
         <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
@@ -2593,19 +2593,19 @@
         <v>130</v>
       </c>
       <c r="AJ11" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
         <v>120</v>
       </c>
       <c r="AL11" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AO11" t="n">
         <v>40</v>
@@ -2644,29 +2644,29 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG11" t="n">
         <v>8.6</v>
       </c>
-      <c r="BD11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -2805,25 +2805,25 @@
         <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
         <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
         <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW12" t="n">
         <v>5.5</v>
@@ -2856,11 +2856,11 @@
         <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
         <v>3.5</v>
@@ -2915,7 +2915,7 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.4</v>
@@ -2924,22 +2924,22 @@
         <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
         <v>1.8</v>
@@ -2951,7 +2951,7 @@
         <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
         <v>85</v>
@@ -2996,7 +2996,7 @@
         <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3032,10 +3032,10 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
@@ -3044,17 +3044,17 @@
         <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
         <v>17.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
@@ -3115,28 +3115,28 @@
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3327,10 +3327,10 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J16" t="n">
         <v>2.88</v>
@@ -3491,13 +3491,13 @@
         <v>3.15</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
         <v>1.44</v>
@@ -3512,19 +3512,19 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
         <v>11</v>
@@ -3533,7 +3533,7 @@
         <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3590,7 +3590,7 @@
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -3602,41 +3602,41 @@
         <v>9</v>
       </c>
       <c r="AW16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX16" t="n">
         <v>5.5</v>
       </c>
-      <c r="AX16" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AY16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>5.2</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BA16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG16" t="n">
         <v>5.8</v>
       </c>
-      <c r="BE16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>1.69</v>
       </c>
       <c r="H17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
         <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -3694,7 +3694,7 @@
         <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
         <v>1.83</v>
@@ -3733,7 +3733,7 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
         <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
         <v>120</v>
@@ -3766,7 +3766,7 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
         <v>970</v>
@@ -3775,16 +3775,16 @@
         <v>180</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="AT17" t="n">
         <v>6.2</v>
@@ -3793,10 +3793,10 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AX17" t="n">
         <v>7.2</v>
@@ -3805,32 +3805,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
         <v>12.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="BF17" t="n">
         <v>9</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,67 +757,67 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="H2" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.44</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.49</v>
-      </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
         <v>2.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
         <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
@@ -847,13 +847,13 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.14</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
         <v>3.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
         <v>4.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.14</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
@@ -1026,13 +1026,13 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1062,13 +1062,13 @@
         <v>3.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
         <v>3.1</v>
@@ -1077,10 +1077,10 @@
         <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
         <v>3.65</v>
@@ -1092,29 +1092,29 @@
         <v>3.9</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
         <v>4.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1214,7 +1214,7 @@
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1259,10 +1259,10 @@
         <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AT4" t="n">
         <v>4.4</v>
@@ -1271,44 +1271,44 @@
         <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G5" t="n">
         <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
         <v>3.25</v>
@@ -1354,31 +1354,31 @@
         <v>2.64</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
         <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="T5" t="n">
         <v>2.12</v>
@@ -1393,10 +1393,10 @@
         <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
         <v>19</v>
@@ -1414,10 +1414,10 @@
         <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
@@ -1429,7 +1429,7 @@
         <v>230</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK5" t="n">
         <v>500</v>
@@ -1450,7 +1450,7 @@
         <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR5" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AU5" t="n">
         <v>3.6</v>
@@ -1471,38 +1471,38 @@
         <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AZ5" t="n">
         <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
         <v>6.2</v>
       </c>
       <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
         <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.94</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
         <v>2.56</v>
@@ -1551,7 +1551,7 @@
         <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
@@ -1563,16 +1563,16 @@
         <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
         <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="T6" t="n">
         <v>2.16</v>
@@ -1584,7 +1584,7 @@
         <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
         <v>13</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AW6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
         <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>90</v>
@@ -1808,7 +1808,7 @@
         <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.6</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -1823,7 +1823,7 @@
         <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
@@ -1844,7 +1844,7 @@
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
         <v>5.7</v>
@@ -1853,10 +1853,10 @@
         <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
@@ -1868,29 +1868,29 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
         <v>6.4</v>
       </c>
       <c r="BC7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5.6</v>
       </c>
-      <c r="BD7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1924,64 +1924,64 @@
         <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -1990,7 +1990,7 @@
         <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,31 +1999,31 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
         <v>9.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
         <v>500</v>
       </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.5</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2035,56 +2035,56 @@
         <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.15</v>
+        <v>11.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>2.16</v>
       </c>
       <c r="AX8" t="n">
         <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.45</v>
+        <v>2.16</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.15</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2115,46 +2115,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="G9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.55</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.6</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2163,10 +2163,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2199,7 +2199,7 @@
         <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>5.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AT9" t="n">
         <v>4.9</v>
@@ -2241,44 +2241,44 @@
         <v>4.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AX9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>1.56</v>
       </c>
-      <c r="AY9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BA9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2378,7 +2378,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AR10" t="n">
         <v>3</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AS10" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="AY10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="BB10" t="n">
         <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="BD10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG10" t="n">
         <v>2.4</v>
       </c>
-      <c r="BE10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2509,40 +2509,40 @@
         <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
         <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
         <v>1.98</v>
@@ -2554,7 +2554,7 @@
         <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X11" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
         <v>130</v>
       </c>
       <c r="AJ11" t="n">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="AK11" t="n">
         <v>120</v>
@@ -2605,7 +2605,7 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AO11" t="n">
         <v>40</v>
@@ -2644,7 +2644,7 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB11" t="n">
         <v>9.199999999999999</v>
@@ -2653,20 +2653,20 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
         <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G12" t="n">
         <v>7.8</v>
@@ -2721,7 +2721,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
         <v>1.3</v>
@@ -2730,13 +2730,13 @@
         <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T12" t="n">
         <v>1.91</v>
@@ -2805,25 +2805,25 @@
         <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR12" t="n">
         <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
         <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW12" t="n">
         <v>5.5</v>
@@ -2844,7 +2844,7 @@
         <v>7.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD12" t="n">
         <v>7.2</v>
@@ -2856,11 +2856,11 @@
         <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.85</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2909,7 +2909,7 @@
         <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -2924,22 +2924,22 @@
         <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
         <v>1.8</v>
@@ -3008,7 +3008,7 @@
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3026,19 +3026,19 @@
         <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
         <v>36</v>
@@ -3047,14 +3047,14 @@
         <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3085,58 +3085,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3279,46 +3279,46 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="J15" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>5.4</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -3327,10 +3327,10 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="I16" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J16" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="K16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
         <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
         <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="X16" t="n">
         <v>11</v>
@@ -3539,7 +3539,7 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
         <v>1000</v>
@@ -3590,10 +3590,10 @@
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>6</v>
@@ -3605,16 +3605,16 @@
         <v>5.8</v>
       </c>
       <c r="AX16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY16" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>5.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>5.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
         <v>6.2</v>
@@ -3626,7 +3626,7 @@
         <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
         <v>6.2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.9</v>
@@ -3685,16 +3685,16 @@
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
         <v>1.83</v>
@@ -3706,7 +3706,7 @@
         <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
         <v>2.08</v>
@@ -3730,7 +3730,7 @@
         <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB17" t="n">
         <v>7.6</v>
@@ -3742,7 +3742,7 @@
         <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF17" t="n">
         <v>970</v>
@@ -3751,10 +3751,10 @@
         <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ17" t="n">
         <v>21</v>
@@ -3769,22 +3769,22 @@
         <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
         <v>6.2</v>
@@ -3793,10 +3793,10 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
         <v>7.2</v>
@@ -3805,32 +3805,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
         <v>12.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G2" t="n">
         <v>1.59</v>
@@ -766,46 +766,46 @@
         <v>7.2</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
         <v>2.68</v>
@@ -817,7 +817,7 @@
         <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
@@ -847,13 +847,13 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AU2" t="n">
         <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB2" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF2" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.55</v>
@@ -978,10 +978,10 @@
         <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
         <v>2.56</v>
@@ -999,10 +999,10 @@
         <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
@@ -1017,13 +1017,13 @@
         <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>60</v>
@@ -1032,7 +1032,7 @@
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1047,7 +1047,7 @@
         <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>11.5</v>
+        <v>2.64</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="O4" t="n">
         <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,22 +1211,22 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AC4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
         <v>500</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1259,10 +1259,10 @@
         <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.23</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.23</v>
+        <v>3.25</v>
       </c>
       <c r="AT4" t="n">
         <v>4.4</v>
@@ -1271,44 +1271,44 @@
         <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.22</v>
+        <v>5.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.23</v>
+        <v>3.35</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.22</v>
+        <v>2.86</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.22</v>
+        <v>2.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.23</v>
+        <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.23</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>3.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>3.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.84</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
         <v>2.56</v>
@@ -1354,7 +1354,7 @@
         <v>2.64</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
         <v>1.61</v>
@@ -1372,7 +1372,7 @@
         <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="R5" t="n">
         <v>1.14</v>
@@ -1387,10 +1387,10 @@
         <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
         <v>8.4</v>
@@ -1429,7 +1429,7 @@
         <v>230</v>
       </c>
       <c r="AJ5" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AK5" t="n">
         <v>500</v>
@@ -1450,59 +1450,59 @@
         <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT5" t="n">
         <v>3.85</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AU5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX5" t="n">
         <v>5</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AY5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA5" t="n">
         <v>6</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="BB5" t="n">
         <v>6</v>
       </c>
-      <c r="AX5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
         <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
         <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
         <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
         <v>6.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1727,85 +1727,85 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
         <v>4.8</v>
       </c>
       <c r="T7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.98</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.83</v>
       </c>
       <c r="V7" t="n">
         <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AF7" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
         <v>500</v>
@@ -1814,10 +1814,10 @@
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ7" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -1829,68 +1829,68 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G8" t="n">
         <v>1.74</v>
@@ -1930,55 +1930,55 @@
         <v>5.9</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
         <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
         <v>500</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>85</v>
+        <v>12.5</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
         <v>5.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.16</v>
+        <v>9.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.14</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>3.35</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.72</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>2.82</v>
       </c>
       <c r="G9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.15</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.52</v>
@@ -2139,146 +2139,146 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
         <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.55</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.59</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.53</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.59</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.57</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.53</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.56</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.59</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.58</v>
+        <v>7.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.59</v>
+        <v>32</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.59</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.58</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.59</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2333,34 +2333,34 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
         <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
         <v>42</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="AR10" t="n">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="AS10" t="n">
-        <v>3</v>
+        <v>1.59</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.92</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.86</v>
+        <v>1.69</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.96</v>
+        <v>2.24</v>
       </c>
       <c r="AY10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>2.68</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="BE10" t="n">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.1</v>
+        <v>1.68</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.55</v>
@@ -2527,7 +2527,7 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.5</v>
@@ -2536,28 +2536,28 @@
         <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R11" t="n">
         <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
         <v>1.42</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
         <v>8.800000000000001</v>
@@ -2569,7 +2569,7 @@
         <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
@@ -2581,22 +2581,22 @@
         <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>340</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AL11" t="n">
         <v>160</v>
@@ -2605,13 +2605,13 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO11" t="n">
         <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
         <v>7.2</v>
@@ -2620,13 +2620,13 @@
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
@@ -2638,35 +2638,35 @@
         <v>17</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE11" t="n">
         <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>7.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="I12" t="n">
         <v>1.69</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K12" t="n">
         <v>4.7</v>
@@ -2721,22 +2721,22 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
         <v>1.91</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2936,16 +2936,16 @@
         <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
         <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y13" t="n">
         <v>12.5</v>
@@ -2954,7 +2954,7 @@
         <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
         <v>8.6</v>
@@ -2978,10 +2978,10 @@
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>65</v>
@@ -3008,7 +3008,7 @@
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3017,44 +3017,44 @@
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>50</v>
+        <v>8.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3085,61 +3085,61 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3163,7 +3163,7 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3279,91 +3279,91 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
         <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.53</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.52</v>
-      </c>
       <c r="Q15" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
         <v>5.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W15" t="n">
         <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>3.6</v>
       </c>
       <c r="H16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
         <v>2.64</v>
@@ -3497,7 +3497,7 @@
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
         <v>1.46</v>
@@ -3539,7 +3539,7 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
         <v>1000</v>
@@ -3584,13 +3584,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR16" t="n">
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -3602,41 +3602,41 @@
         <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF16" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
         <v>3.9</v>
@@ -3691,28 +3691,28 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
         <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
@@ -3730,31 +3730,31 @@
         <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG17" t="n">
         <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
         <v>21</v>
@@ -3763,74 +3763,74 @@
         <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AQ17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT17" t="n">
         <v>5.6</v>
       </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
       <c r="AX17" t="n">
         <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB17" t="n">
         <v>12.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.58</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2.06</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>1.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>730</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>760</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>790</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.7</v>
+        <v>1.19</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.85</v>
+        <v>1.42</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.35</v>
+        <v>1.26</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.55</v>
+        <v>1.42</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.85</v>
+        <v>1.26</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.8</v>
+        <v>1.23</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.85</v>
+        <v>1.36</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,102 +937,102 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.34</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.48</v>
       </c>
-      <c r="H3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.72</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.67</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
         <v>11</v>
       </c>
-      <c r="Y3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1041,87 +1041,87 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW3" t="n">
         <v>3.45</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>3.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,78 +1131,78 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
         <v>2.64</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
         <v>1.6</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,22 +1211,22 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>160</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>1.07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>1.05</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.25</v>
+        <v>1.09</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>1.17</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.8</v>
+        <v>1.05</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="AX4" t="n">
-        <v>3</v>
+        <v>1.09</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.86</v>
+        <v>1.17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.96</v>
+        <v>1.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.96</v>
+        <v>1.09</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.1</v>
+        <v>1.74</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>1.09</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.55</v>
+        <v>1.05</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1330,112 +1330,112 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="X5" t="n">
-        <v>8.4</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>160</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>2.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.9</v>
+        <v>2.54</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AY5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1524,34 +1524,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Club El Porvenir</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
         <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
@@ -1560,25 +1560,25 @@
         <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
         <v>1.45</v>
@@ -1587,49 +1587,49 @@
         <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1641,69 +1641,69 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX6" t="n">
         <v>5</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AY6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA6" t="n">
         <v>6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="BB6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD6" t="n">
         <v>6</v>
       </c>
-      <c r="AX6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BE6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Club El Porvenir</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>3.75</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>5.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="n">
         <v>5.9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="AV8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.82</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>1.77</v>
       </c>
       <c r="H9" t="n">
-        <v>2.82</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8</v>
-      </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA9" t="n">
         <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,72 +2295,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Sportivo AC Las Parejas</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2375,11 +2375,11 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
         <v>500</v>
       </c>
-      <c r="AC10" t="n">
-        <v>42</v>
-      </c>
       <c r="AD10" t="n">
         <v>1000</v>
       </c>
@@ -2411,75 +2411,75 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.44</v>
+        <v>1.17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.98</v>
+        <v>1.17</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.2</v>
+        <v>1.16</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>1.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.24</v>
+        <v>1.17</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.36</v>
+        <v>1.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.68</v>
+        <v>1.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.81</v>
+        <v>1.19</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I11" t="n">
         <v>3.35</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.76</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
         <v>20</v>
       </c>
-      <c r="AG11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL11" t="n">
         <v>55</v>
       </c>
-      <c r="AL11" t="n">
-        <v>160</v>
-      </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="n">
         <v>40</v>
       </c>
-      <c r="AP11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CA Mineiro (W)</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sao Paulo (W)</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.3</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>1.57</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>1.69</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
         <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
       </c>
       <c r="S12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X12" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>3.15</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AR12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.91</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>260</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF12" t="n">
-        <v>7.4</v>
+        <v>2.76</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>1.86</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.3</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP13" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AQ13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="AS13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>14</v>
-      </c>
       <c r="AW13" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY13" t="n">
         <v>11</v>
       </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG13" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,117 +3071,117 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CA Mineiro (W)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Sao Paulo (W)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.77</v>
+        <v>5.3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.83</v>
+        <v>7.8</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>1.55</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.36</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S14" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
         <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>2.48</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3190,72 +3190,72 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>5.9</v>
       </c>
-      <c r="AV14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="BA14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB14" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA14" t="n">
+      <c r="BC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>11</v>
-      </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="K15" t="n">
         <v>3.5</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="X15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10</v>
-      </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU15" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AV15" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX15" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,114 +3459,114 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.45</v>
+        <v>1.65</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.64</v>
+        <v>8.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.61</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="X16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
         <v>11</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,75 +3575,75 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT16" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10</v>
-      </c>
       <c r="AU16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD16" t="n">
         <v>6</v>
       </c>
-      <c r="AV16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB16" t="n">
+      <c r="BE16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD16" t="n">
+      <c r="BF16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,572 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22:20:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.65</v>
+        <v>3.75</v>
       </c>
       <c r="G17" t="n">
-        <v>1.68</v>
+        <v>4.2</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>2.38</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="R17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.32</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.44</v>
-      </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG17" t="n">
         <v>21</v>
       </c>
-      <c r="Z17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>970</v>
-      </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ17" t="n">
         <v>6.4</v>
       </c>
       <c r="AR17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-30 07:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY18" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="AZ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-30 07:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>22:20:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG19" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-03-30 04:58:23</t>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>1.11</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1011,7 +1011,7 @@
         <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1020,7 +1020,7 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
         <v>950</v>
@@ -1044,7 +1044,7 @@
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.2</v>
+        <v>2.36</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.5</v>
+        <v>2.22</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.45</v>
+        <v>1.88</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.5</v>
+        <v>2.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.45</v>
+        <v>1.88</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.2</v>
+        <v>2.16</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.9</v>
+        <v>2.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>2.08</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
         <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>2.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.52</v>
+        <v>5.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.07</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.05</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.09</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.17</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.05</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.09</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.09</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.17</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.17</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.09</v>
+        <v>42</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.74</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.09</v>
+        <v>26</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.09</v>
+        <v>42</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.09</v>
+        <v>95</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.05</v>
+        <v>32</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.05</v>
+        <v>38</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
         <v>2.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1432,7 +1432,7 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>1.89</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="AT5" t="n">
         <v>4.4</v>
@@ -1465,44 +1465,44 @@
         <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>1.71</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.54</v>
+        <v>1.46</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.7</v>
+        <v>1.86</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>1.81</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.4</v>
+        <v>1.88</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>1.84</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>1.72</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>1.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>1.89</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1533,103 +1533,103 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="G6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.65</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>4.9</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
         <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1644,59 +1644,59 @@
         <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.7</v>
+        <v>1.47</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.8</v>
+        <v>1.56</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.8</v>
+        <v>1.62</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.55</v>
+        <v>1.47</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.7</v>
+        <v>1.62</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.7</v>
+        <v>1.55</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.2</v>
+        <v>1.59</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>1.63</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.9</v>
+        <v>1.62</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.8</v>
+        <v>1.62</v>
       </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>1.63</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>1.63</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.8</v>
+        <v>1.63</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1727,79 +1727,79 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="H7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J7" t="n">
         <v>2.56</v>
       </c>
-      <c r="I7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.6</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.84</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>5.2</v>
+        <v>1.63</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>1.58</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.85</v>
+        <v>1.59</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>1.59</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>1.58</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>1.52</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.8</v>
+        <v>1.54</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.4</v>
+        <v>1.88</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>1.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>1.61</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>1.59</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>1.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>1.99</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.2</v>
+        <v>1.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1930,19 +1930,19 @@
         <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L8" t="n">
         <v>1.52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1960,25 +1960,25 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -1987,13 +1987,13 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
@@ -2014,28 +2014,28 @@
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>250</v>
+        <v>460</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
         <v>8.800000000000001</v>
@@ -2044,7 +2044,7 @@
         <v>5</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
         <v>9</v>
@@ -2053,38 +2053,38 @@
         <v>8.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
         <v>15</v>
       </c>
       <c r="BB8" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
         <v>7</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="G9" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2142,85 +2142,85 @@
         <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
         <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="X9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK9" t="n">
         <v>21</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AL9" t="n">
         <v>40</v>
       </c>
-      <c r="AG9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
@@ -2229,56 +2229,56 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>2.08</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
         <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>1.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AC10" t="n">
         <v>500</v>
@@ -2390,7 +2390,7 @@
         <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2402,7 +2402,7 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BF10" t="n">
         <v>1.55</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -2527,13 +2527,13 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
         <v>2.34</v>
@@ -2545,128 +2545,128 @@
         <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AO11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX11" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>9.6</v>
       </c>
       <c r="BB11" t="n">
         <v>14.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="BE11" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="BF11" t="n">
         <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>3.45</v>
@@ -2715,19 +2715,19 @@
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
@@ -2736,131 +2736,131 @@
         <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
         <v>1.87</v>
       </c>
       <c r="X12" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
         <v>500</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AF12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG12" t="n">
         <v>500</v>
       </c>
-      <c r="AC12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>500</v>
       </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>900</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.98</v>
+        <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.64</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.58</v>
+        <v>6.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.26</v>
+        <v>5.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.91</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.76</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2894,58 +2894,58 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
         <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
         <v>9</v>
@@ -2954,10 +2954,10 @@
         <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>7.4</v>
@@ -2969,16 +2969,16 @@
         <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ13" t="n">
         <v>70</v>
@@ -2987,7 +2987,7 @@
         <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2996,7 +2996,7 @@
         <v>65</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
         <v>8.6</v>
@@ -3008,53 +3008,53 @@
         <v>13.5</v>
       </c>
       <c r="AS13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>17.5</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BA13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG13" t="n">
         <v>8</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G14" t="n">
         <v>7.8</v>
@@ -3097,10 +3097,10 @@
         <v>1.67</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
@@ -3124,13 +3124,13 @@
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V14" t="n">
         <v>2.48</v>
@@ -3142,7 +3142,7 @@
         <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z14" t="n">
         <v>10</v>
@@ -3154,16 +3154,16 @@
         <v>23</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG14" t="n">
         <v>28</v>
@@ -3178,10 +3178,10 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AL14" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>10.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA14" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD14" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
@@ -3297,7 +3297,7 @@
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
@@ -3306,109 +3306,109 @@
         <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P15" t="n">
         <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X15" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO15" t="n">
         <v>65</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>75</v>
-      </c>
       <c r="AP15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT15" t="n">
         <v>7.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
@@ -3420,29 +3420,29 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="H16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
         <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="X16" t="n">
         <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I17" t="n">
         <v>2.38</v>
@@ -3682,7 +3682,7 @@
         <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
         <v>1.56</v>
@@ -3691,7 +3691,7 @@
         <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O17" t="n">
         <v>1.51</v>
@@ -3700,7 +3700,7 @@
         <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
         <v>1.21</v>
@@ -3712,31 +3712,31 @@
         <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
         <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AA17" t="n">
         <v>40</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
         <v>14.5</v>
@@ -3745,13 +3745,13 @@
         <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
         <v>70</v>
@@ -3775,62 +3775,62 @@
         <v>38</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
         <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17" t="n">
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
         <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -3861,67 +3861,67 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
         <v>3.65</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="J18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L18" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
         <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
@@ -3933,7 +3933,7 @@
         <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3942,10 +3942,10 @@
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG18" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC18" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -4055,37 +4055,37 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="H19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I19" t="n">
         <v>6.4</v>
       </c>
-      <c r="I19" t="n">
-        <v>7.2</v>
-      </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
         <v>2.1</v>
@@ -4094,131 +4094,131 @@
         <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI19" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM19" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AP19" t="n">
         <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
         <v>1.1</v>
@@ -975,22 +975,22 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.5</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1008,7 +1008,7 @@
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1020,10 +1020,10 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1044,7 +1044,7 @@
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.12</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.36</v>
+        <v>1.42</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AX3" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.14</v>
+        <v>1.34</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.12</v>
+        <v>1.34</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.16</v>
+        <v>1.42</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.36</v>
+        <v>1.42</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
         <v>5.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE4" t="n">
         <v>60</v>
       </c>
-      <c r="AB4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>48</v>
-      </c>
       <c r="AF4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
       </c>
       <c r="AI4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO4" t="n">
         <v>75</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS4" t="n">
         <v>60</v>
       </c>
-      <c r="AP4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>28</v>
-      </c>
       <c r="AT4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BB4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD4" t="n">
         <v>42</v>
       </c>
       <c r="BE4" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="BF4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BG4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H5" t="n">
         <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>2.46</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1450,13 +1450,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.89</v>
+        <v>8.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.49</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
         <v>4.4</v>
@@ -1465,44 +1465,44 @@
         <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.71</v>
+        <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.46</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.86</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.81</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.49</v>
+        <v>3.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.88</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.84</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.72</v>
+        <v>3.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.72</v>
+        <v>3.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.89</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.89</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1533,103 +1533,103 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
         <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1644,59 +1644,59 @@
         <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.47</v>
+        <v>3.85</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.56</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.62</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.62</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.57</v>
+        <v>5.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.59</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.63</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.62</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.62</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.63</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.63</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.63</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
       <c r="R7" t="n">
         <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.58</v>
+        <v>3.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.58</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.59</v>
+        <v>3.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.59</v>
+        <v>5.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.58</v>
+        <v>6.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.52</v>
+        <v>5.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.88</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.62</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.61</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.59</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.62</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.99</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.62</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.62</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
         <v>1.52</v>
@@ -1948,34 +1948,34 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>90</v>
@@ -1987,10 +1987,10 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
@@ -2005,7 +2005,7 @@
         <v>21</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AL8" t="n">
         <v>460</v>
@@ -2023,34 +2023,34 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>6.4</v>
@@ -2059,32 +2059,32 @@
         <v>7.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>90</v>
       </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G9" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.7</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.6</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.7</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL9" t="n">
         <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BD9" t="n">
         <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>65</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2309,46 +2309,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="K10" t="n">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2357,10 +2357,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2402,7 +2402,7 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AU10" t="n">
         <v>1.23</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AV10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY10" t="n">
         <v>1.23</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BA10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC10" t="n">
         <v>1.25</v>
       </c>
-      <c r="BB10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BD10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BF10" t="n">
         <v>1.55</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -2530,143 +2530,143 @@
         <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.9</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
         <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
         <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BD11" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.7</v>
+        <v>55</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
         <v>4.1</v>
@@ -2712,7 +2712,7 @@
         <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.43</v>
@@ -2724,31 +2724,31 @@
         <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
         <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X12" t="n">
         <v>90</v>
@@ -2772,7 +2772,7 @@
         <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AF12" t="n">
         <v>40</v>
@@ -2799,7 +2799,7 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -2814,31 +2814,31 @@
         <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12" t="n">
         <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
@@ -2847,20 +2847,20 @@
         <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="BF12" t="n">
         <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
         <v>3.4</v>
@@ -2900,7 +2900,7 @@
         <v>2.62</v>
       </c>
       <c r="I13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
@@ -2921,10 +2921,10 @@
         <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
         <v>1.23</v>
@@ -2933,16 +2933,16 @@
         <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
         <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
         <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB13" t="n">
         <v>9.800000000000001</v>
@@ -2978,7 +2978,7 @@
         <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
         <v>70</v>
@@ -2987,7 +2987,7 @@
         <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3026,16 +3026,16 @@
         <v>17</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>28</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
@@ -3047,14 +3047,14 @@
         <v>46</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I14" t="n">
         <v>1.67</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3118,7 +3118,7 @@
         <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
@@ -3130,28 +3130,28 @@
         <v>1.91</v>
       </c>
       <c r="U14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V14" t="n">
         <v>2.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z14" t="n">
         <v>10</v>
       </c>
       <c r="AA14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
@@ -3163,16 +3163,16 @@
         <v>18.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG14" t="n">
         <v>28</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
@@ -3181,7 +3181,7 @@
         <v>700</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3190,65 +3190,65 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD14" t="n">
         <v>8</v>
       </c>
-      <c r="BC14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.5</v>
@@ -3309,10 +3309,10 @@
         <v>1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
@@ -3321,94 +3321,94 @@
         <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
         <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
@@ -3420,29 +3420,29 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BC15" t="n">
         <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BF15" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3473,61 +3473,61 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G16" t="n">
         <v>1.66</v>
       </c>
       <c r="H16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R16" t="n">
         <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.93</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
         <v>23</v>
@@ -3539,10 +3539,10 @@
         <v>230</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>29</v>
@@ -3554,7 +3554,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>22</v>
@@ -3575,7 +3575,7 @@
         <v>170</v>
       </c>
       <c r="AN16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>150</v>
@@ -3584,25 +3584,25 @@
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AW16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -3614,29 +3614,29 @@
         <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BE16" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3667,46 +3667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G17" t="n">
         <v>3.7</v>
       </c>
-      <c r="G17" t="n">
-        <v>4.1</v>
-      </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="I17" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
         <v>2.04</v>
@@ -3715,52 +3715,52 @@
         <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X17" t="n">
         <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
         <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3772,22 +3772,22 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
         <v>6.2</v>
@@ -3796,41 +3796,41 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.7</v>
+        <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.1</v>
+        <v>55</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>22</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3864,49 +3864,49 @@
         <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H18" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
         <v>2.54</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
         <v>3.25</v>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
         <v>1.64</v>
@@ -3918,10 +3918,10 @@
         <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
@@ -3930,10 +3930,10 @@
         <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3969,16 +3969,16 @@
         <v>34</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -3987,44 +3987,44 @@
         <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I19" t="n">
         <v>6.4</v>
@@ -4070,28 +4070,28 @@
         <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
         <v>3.85</v>
@@ -4100,10 +4100,10 @@
         <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W19" t="n">
         <v>2.32</v>
@@ -4115,40 +4115,40 @@
         <v>18.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA19" t="n">
         <v>170</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
         <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
         <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
         <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
         <v>42</v>
@@ -4157,22 +4157,22 @@
         <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
         <v>7</v>
@@ -4181,10 +4181,10 @@
         <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX19" t="n">
         <v>8.800000000000001</v>
@@ -4193,10 +4193,10 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB19" t="n">
         <v>15.5</v>
@@ -4208,7 +4208,7 @@
         <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF19" t="n">
         <v>11</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.06</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.58</v>
+        <v>2.78</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>2.96</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,146 +781,146 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>760</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>750</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>1.01</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>730</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>760</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>790</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>2.14</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.36</v>
+        <v>2.52</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>2.42</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
         <v>1.1</v>
@@ -966,28 +966,28 @@
         <v>1.11</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
         <v>1.05</v>
@@ -999,10 +999,10 @@
         <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.4</v>
+        <v>2.04</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.34</v>
+        <v>2.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H4" t="n">
         <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
@@ -1163,58 +1163,58 @@
         <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R4" t="n">
         <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="n">
         <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4" t="n">
         <v>16</v>
@@ -1229,13 +1229,13 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
         <v>34</v>
@@ -1244,16 +1244,16 @@
         <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.4</v>
@@ -1262,16 +1262,16 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU4" t="n">
         <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>48</v>
@@ -1283,10 +1283,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1295,20 +1295,20 @@
         <v>28</v>
       </c>
       <c r="BD4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BE4" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="BF4" t="n">
         <v>28</v>
       </c>
       <c r="BG4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
         <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
         <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X5" t="n">
         <v>500</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR5" t="n">
         <v>8.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
         <v>4.4</v>
@@ -1468,7 +1468,7 @@
         <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
@@ -1480,29 +1480,29 @@
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
         <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1533,55 +1533,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
@@ -1590,37 +1590,37 @@
         <v>7.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA6" t="n">
         <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AJ6" t="n">
         <v>200</v>
@@ -1638,65 +1638,65 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AX6" t="n">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
         <v>6.6</v>
       </c>
       <c r="BC6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1727,88 +1727,88 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
         <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="M7" t="n">
         <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
         <v>3.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>7.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>60</v>
+        <v>7.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS7" t="n">
         <v>6.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW7" t="n">
         <v>6.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD7" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
         <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC8" t="n">
         <v>25</v>
       </c>
-      <c r="AO8" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13</v>
-      </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2115,97 +2115,97 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="X9" t="n">
         <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AA9" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK9" t="n">
         <v>19.5</v>
@@ -2214,34 +2214,34 @@
         <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
         <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AS9" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
@@ -2250,35 +2250,35 @@
         <v>8.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC9" t="n">
         <v>16</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG9" t="n">
         <v>15.5</v>
       </c>
-      <c r="BD9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>65</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -2345,7 +2345,7 @@
         <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2378,7 +2378,7 @@
         <v>120</v>
       </c>
       <c r="AC10" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AV10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AZ10" t="n">
         <v>1.27</v>
       </c>
-      <c r="AT10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="BA10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC10" t="n">
         <v>1.27</v>
       </c>
-      <c r="AX10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BD10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF10" t="n">
         <v>1.55</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
@@ -2527,31 +2527,31 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
         <v>1.56</v>
@@ -2563,58 +2563,58 @@
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
         <v>18.5</v>
@@ -2623,25 +2623,25 @@
         <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
         <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>38</v>
@@ -2650,23 +2650,23 @@
         <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BF11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>1.43</v>
@@ -2727,10 +2727,10 @@
         <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2739,128 +2739,128 @@
         <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
         <v>27</v>
       </c>
-      <c r="AC12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE12" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF12" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
         <v>3.4</v>
@@ -2900,10 +2900,10 @@
         <v>2.62</v>
       </c>
       <c r="I13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
@@ -2918,7 +2918,7 @@
         <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
         <v>1.66</v>
@@ -2933,13 +2933,13 @@
         <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
         <v>1.41</v>
@@ -2954,7 +2954,7 @@
         <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB13" t="n">
         <v>9.800000000000001</v>
@@ -3020,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
         <v>17</v>
@@ -3029,7 +3029,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
         <v>28</v>
@@ -3044,17 +3044,17 @@
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H14" t="n">
         <v>1.56</v>
@@ -3103,7 +3103,7 @@
         <v>4.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3115,22 +3115,22 @@
         <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
         <v>1.91</v>
       </c>
       <c r="U14" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
         <v>2.48</v>
@@ -3154,7 +3154,7 @@
         <v>24</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
@@ -3187,10 +3187,10 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
@@ -3232,13 +3232,13 @@
         <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD14" t="n">
         <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="BF14" t="n">
         <v>8.199999999999999</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H15" t="n">
         <v>3.6</v>
@@ -3303,82 +3303,82 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y15" t="n">
         <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
         <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
         <v>22</v>
@@ -3387,62 +3387,62 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
         <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BB15" t="n">
         <v>25</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="BF15" t="n">
         <v>18.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>1.63</v>
       </c>
       <c r="G16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H16" t="n">
         <v>7.2</v>
       </c>
       <c r="I16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
         <v>3.8</v>
@@ -3500,25 +3500,25 @@
         <v>3.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
         <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.96</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.93</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
@@ -3527,7 +3527,7 @@
         <v>2.5</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y16" t="n">
         <v>23</v>
@@ -3560,7 +3560,7 @@
         <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ16" t="n">
         <v>16</v>
@@ -3575,22 +3575,22 @@
         <v>170</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO16" t="n">
         <v>150</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>7.2</v>
@@ -3620,23 +3620,23 @@
         <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD16" t="n">
         <v>17</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3667,46 +3667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="I17" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="J17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T17" t="n">
         <v>2.04</v>
@@ -3715,25 +3715,25 @@
         <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
         <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
         <v>7.6</v>
@@ -3745,10 +3745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
         <v>26</v>
@@ -3760,7 +3760,7 @@
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3772,65 +3772,65 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR17" t="n">
         <v>12.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU17" t="n">
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>48</v>
       </c>
       <c r="BB17" t="n">
-        <v>55</v>
+        <v>5.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.5</v>
@@ -3894,7 +3894,7 @@
         <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
@@ -3903,10 +3903,10 @@
         <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
         <v>1.64</v>
@@ -3927,13 +3927,13 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC18" t="n">
         <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3942,7 +3942,7 @@
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX18" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX18" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY18" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -4055,97 +4055,97 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="H19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
         <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG19" t="n">
         <v>970</v>
       </c>
-      <c r="AC19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AK19" t="n">
         <v>19</v>
@@ -4157,25 +4157,25 @@
         <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU19" t="n">
         <v>8</v>
@@ -4187,38 +4187,38 @@
         <v>13</v>
       </c>
       <c r="AX19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY19" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H2" t="n">
         <v>3.5</v>
       </c>
-      <c r="G2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.66</v>
       </c>
-      <c r="I2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>760</v>
+        <v>19.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>750</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>70</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.42</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>110</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.14</v>
+        <v>50</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.14</v>
+        <v>110</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.52</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.05</v>
+        <v>65</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.42</v>
+        <v>100</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,75 +937,75 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.53</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
         <v>1000</v>
@@ -1029,10 +1029,10 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1041,7 +1041,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
         <v>1000</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.04</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.68</v>
+        <v>4.9</v>
       </c>
       <c r="AR3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.69</v>
       </c>
-      <c r="AS3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AU3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.56</v>
+        <v>1.99</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.4</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.76</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC4" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS4" t="n">
         <v>24</v>
       </c>
-      <c r="AI4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX4" t="n">
         <v>20</v>
       </c>
-      <c r="AS4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>65</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="n">
-        <v>95</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>60</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -1330,88 +1330,88 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>Club El Porvenir</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.98</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="X5" t="n">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1432,7 +1432,7 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD5" t="n">
         <v>6.6</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB5" t="n">
+      <c r="BE5" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.25</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.84</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.94</v>
+        <v>2.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="X6" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
         <v>8</v>
       </c>
-      <c r="Z6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
         <v>500</v>
       </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="n">
         <v>7.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>46</v>
       </c>
       <c r="AX6" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>60</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>160</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Club El Porvenir</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>1.58</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>1.59</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.37</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>2.66</v>
       </c>
       <c r="X7" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF7" t="n">
         <v>9</v>
       </c>
-      <c r="AC7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>500</v>
-      </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT7" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AU7" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>85</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>80</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sportivo AC Las Parejas</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.11</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.94</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>160</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT8" t="n">
         <v>1.69</v>
       </c>
-      <c r="X8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>1.55</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>1.76</v>
       </c>
       <c r="AW8" t="n">
-        <v>38</v>
+        <v>1.79</v>
       </c>
       <c r="AX8" t="n">
-        <v>12.5</v>
+        <v>1.68</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>1.68</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>1.75</v>
       </c>
       <c r="BA8" t="n">
-        <v>48</v>
+        <v>1.79</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>1.78</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>1.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>38</v>
+        <v>1.78</v>
       </c>
       <c r="BE8" t="n">
-        <v>16.5</v>
+        <v>1.79</v>
       </c>
       <c r="BF8" t="n">
-        <v>22</v>
+        <v>1.74</v>
       </c>
       <c r="BG8" t="n">
-        <v>14.5</v>
+        <v>1.79</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>2.66</v>
       </c>
       <c r="H9" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z9" t="n">
         <v>22</v>
       </c>
-      <c r="Z9" t="n">
-        <v>130</v>
-      </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC9" t="n">
         <v>27</v>
       </c>
-      <c r="AE9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="BD9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG9" t="n">
         <v>40</v>
       </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Escobar FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sportivo AC Las Parejas</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="G10" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.65</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>120</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>130</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.27</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.27</v>
+        <v>8.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.28</v>
+        <v>16</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.29</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.25</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.27</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.29</v>
+        <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.27</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.25</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.27</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.29</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.28</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.27</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.29</v>
+        <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.29</v>
+        <v>85</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.1</v>
       </c>
-      <c r="I11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.43</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.56</v>
-      </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV11" t="n">
         <v>11</v>
       </c>
-      <c r="Z11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AW11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY11" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="BG11" t="n">
         <v>30</v>
       </c>
-      <c r="BE11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>36</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CA Mineiro (W)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Sao Paulo (W)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.95</v>
+        <v>6.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>1.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>2.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.96</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AX12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>10</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.4</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="X13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY13" t="n">
         <v>10</v>
       </c>
-      <c r="Y13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE13" t="n">
         <v>15</v>
       </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>130</v>
-      </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CA Mineiro (W)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sao Paulo (W)</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.2</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>7.8</v>
+        <v>1.69</v>
       </c>
       <c r="H14" t="n">
-        <v>1.56</v>
+        <v>6.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.67</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.9</v>
       </c>
-      <c r="K14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.91</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>2.48</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AX14" t="n">
         <v>8.4</v>
       </c>
-      <c r="Z14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC14" t="n">
         <v>16</v>
       </c>
-      <c r="AB14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>8</v>
-      </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="BE14" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="X15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR15" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AS15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT15" t="n">
         <v>8</v>
       </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW15" t="n">
         <v>29</v>
       </c>
-      <c r="AK15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>22</v>
-      </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BB15" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BD15" t="n">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>18.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>42</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.63</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>1.67</v>
+        <v>3.7</v>
       </c>
       <c r="H16" t="n">
-        <v>7.2</v>
+        <v>2.42</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>2.54</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="P16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="AR16" t="n">
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF16" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB16" t="n">
+      <c r="BG16" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,572 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:20:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="H17" t="n">
-        <v>2.54</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>2.74</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>2.52</v>
       </c>
       <c r="X17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN17" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AO17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>19</v>
       </c>
-      <c r="AA17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AR17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB17" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="BC17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE17" t="n">
         <v>19</v>
       </c>
-      <c r="BA17" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF17" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Central Espanol</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Deportivo Maldonado</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-03-30 13:22:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>22:20:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fortaleza FC</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="X19" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>CA Lugano</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>180</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="J2" t="n">
-        <v>2.84</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>100</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.6</v>
+        <v>220</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>220</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>220</v>
       </c>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>220</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>220</v>
       </c>
       <c r="AV2" t="n">
-        <v>16.5</v>
+        <v>220</v>
       </c>
       <c r="AW2" t="n">
-        <v>70</v>
+        <v>1.14</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>220</v>
       </c>
       <c r="AZ2" t="n">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="BA2" t="n">
-        <v>110</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="BC2" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="BD2" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="BF2" t="n">
-        <v>65</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -942,79 +942,79 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CA Lugano</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>2.42</v>
+        <v>720</v>
       </c>
       <c r="H3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>690</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.85</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.82</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="S3" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB3" t="n">
         <v>1000</v>
@@ -1023,19 +1023,19 @@
         <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AR3" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR3" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AS3" t="n">
-        <v>1.75</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="AU3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AV3" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AW3" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.7</v>
+        <v>2.96</v>
       </c>
       <c r="AY3" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.66</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.82</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.69</v>
+        <v>2.96</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.49</v>
+        <v>2.64</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>Club El Porvenir</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA4" t="n">
         <v>3.4</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BB4" t="n">
-        <v>8</v>
+        <v>220</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>8</v>
+        <v>2.98</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>3.05</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.199999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,76 +1330,76 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Club El Porvenir</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>50</v>
       </c>
       <c r="K5" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1408,10 +1408,10 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>20</v>
+        <v>1.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.5</v>
+        <v>220</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>220</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>1.05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>1.08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>250</v>
       </c>
       <c r="I6" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1.1</v>
       </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>5.2</v>
       </c>
       <c r="P6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.42</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="S6" t="n">
-        <v>4.9</v>
+        <v>29</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8</v>
+        <v>1.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>7</v>
+        <v>790</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>800</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.4</v>
+        <v>220</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="AS6" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>1.02</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>2.86</v>
       </c>
       <c r="AW6" t="n">
-        <v>46</v>
+        <v>2.86</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>60</v>
+        <v>2.86</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>27</v>
+        <v>5.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>44</v>
+        <v>2.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>160</v>
+        <v>2.86</v>
       </c>
       <c r="BF6" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>55</v>
+        <v>2.86</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,78 +1713,78 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Sportivo AC Las Parejas</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.59</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S7" t="n">
         <v>7.8</v>
       </c>
-      <c r="J7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>2.66</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,111 +1793,111 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
         <v>110</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AQ7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AR7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AS7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.4</v>
+        <v>220</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>85</v>
+        <v>1.64</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.4</v>
+        <v>220</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>80</v>
+        <v>1.68</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>1.63</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>1.68</v>
       </c>
       <c r="BE7" t="n">
-        <v>48</v>
+        <v>1.69</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="BG7" t="n">
-        <v>15</v>
+        <v>1.69</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Escobar FC</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sportivo AC Las Parejas</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
         <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.35</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="R8" t="n">
         <v>1.13</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="n">
-        <v>160</v>
+        <v>8.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>400</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO8" t="n">
         <v>120</v>
       </c>
-      <c r="AC8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>190</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP8" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.64</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.76</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.79</v>
+        <v>55</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.69</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.76</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.79</v>
+        <v>46</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.68</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.68</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.75</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.79</v>
+        <v>85</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.78</v>
+        <v>38</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.75</v>
+        <v>38</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.78</v>
+        <v>80</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.79</v>
+        <v>200</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.74</v>
+        <v>50</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.79</v>
+        <v>80</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AH9" t="n">
         <v>22</v>
       </c>
-      <c r="AA9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AI9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL9" t="n">
         <v>44</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>29</v>
-      </c>
       <c r="AO9" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AP9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="AZ9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC9" t="n">
         <v>19</v>
       </c>
-      <c r="AS9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>27</v>
-      </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="BF9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BG9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.06</v>
       </c>
-      <c r="H10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="U10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.43</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.94</v>
-      </c>
       <c r="X10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR10" t="n">
         <v>14</v>
       </c>
-      <c r="Y10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AS10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD10" t="n">
         <v>42</v>
       </c>
-      <c r="AI10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>24</v>
-      </c>
       <c r="BE10" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="BF10" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="BG10" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>CA Mineiro (W)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Sao Paulo (W)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="I11" t="n">
-        <v>2.72</v>
+        <v>1.71</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.2</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="V11" t="n">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>46</v>
+        <v>17.5</v>
       </c>
       <c r="AB11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AE11" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="AP11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="AW11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>30</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CA Mineiro (W)</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sao Paulo (W)</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.4</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.54</v>
+        <v>3.65</v>
       </c>
       <c r="I12" t="n">
-        <v>1.65</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>2.52</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS12" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AT12" t="n">
         <v>8.4</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY12" t="n">
         <v>10</v>
       </c>
-      <c r="AA12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>260</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>21</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>80</v>
+        <v>13.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.6</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.45</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AO13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP13" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AQ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>25</v>
       </c>
-      <c r="AA13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>22</v>
-      </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
-        <v>18.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.69</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW14" t="n">
         <v>6.6</v>
       </c>
-      <c r="I14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X14" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="H15" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="I15" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
         <v>9</v>
       </c>
-      <c r="Z15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW15" t="n">
         <v>11</v>
       </c>
-      <c r="AW15" t="n">
-        <v>29</v>
-      </c>
       <c r="AX15" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>48</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BC15" t="n">
-        <v>40</v>
+        <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,378 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:20:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.7</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>2.56</v>
       </c>
       <c r="X16" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC16" t="n">
         <v>9</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AD16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS16" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>25</v>
-      </c>
       <c r="AT16" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>16</v>
       </c>
-      <c r="BA16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BD16" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>22:20:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fortaleza FC</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="X17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.29</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>1.31</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>1.39</v>
       </c>
       <c r="I2" t="n">
-        <v>44</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,67 +781,67 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
         <v>4.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -850,84 +850,84 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.87</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="AR2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AT2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AX2" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="AY2" t="n">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="BA2" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="BB2" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="BC2" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.77</v>
+        <v>70</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.95</v>
+        <v>120</v>
       </c>
       <c r="BG2" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CA Mineiro (W)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sao Paulo (W)</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.95</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="L3" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S3" t="n">
+        <v>23</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.15</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.89</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>34</v>
+        <v>530</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>540</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA3" t="n">
         <v>14</v>
       </c>
-      <c r="AE3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>380</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="BB3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC3" t="n">
         <v>55</v>
       </c>
-      <c r="AP3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>95</v>
-      </c>
       <c r="BD3" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="BE3" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="BF3" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="BG3" t="n">
         <v>23</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>1.47</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>13.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>15.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>2.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>180</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>110</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>280</v>
+      </c>
+      <c r="BF4" t="n">
         <v>55</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BG4" t="n">
         <v>50</v>
       </c>
-      <c r="AT4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>36</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.94</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>2.74</v>
+        <v>1.41</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>1.42</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>50</v>
-      </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>400</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>460</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>20</v>
       </c>
-      <c r="AG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BA5" t="n">
         <v>55</v>
       </c>
-      <c r="AL5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY5" t="n">
+      <c r="BB5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC5" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="BE5" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.74</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>790</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>220</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD6" t="n">
         <v>22</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>12</v>
-      </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>1.51</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,572 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:20:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.15</v>
+        <v>1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>7.2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.82</v>
+        <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
         <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>2.74</v>
       </c>
       <c r="X7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>670</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AZ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA7" t="n">
         <v>55</v>
       </c>
-      <c r="AB7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>110</v>
       </c>
       <c r="BF7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>80</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Central Espanol</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Deportivo Maldonado</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-03-30 19:40:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>22:20:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fortaleza FC</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X9" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>310</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
